--- a/tests/fixtures/ml-real-publish-test.xlsx
+++ b/tests/fixtures/ml-real-publish-test.xlsx
@@ -571,7 +571,7 @@
         <v>no</v>
       </c>
       <c r="T2" t="str">
-        <v>https://images.samsung.com/is/image/samsung/latin-en-rt29faradww-cl-001-front-white.jpg|https://images.samsung.com/is/image/samsung/latin-en-rt29faradww-cl-002-open-white.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/8/89/Refrigerator.jpg|https://upload.wikimedia.org/wikipedia/commons/b/b8/Fridge.jpg</v>
       </c>
       <c r="U2" t="str">
         <v>Heladera Samsung No Frost RT29FARADWW de 290 litros. Tecnologia No Frost: elimina la escarcha automaticamente. Capacidad total: 290 litros (210L heladera + 80L freezer). Panel de control en la puerta. Alarma de puerta abierta. Iluminacion LED interior. Estantes de vidrio templado. Incluye garantia oficial Samsung de 12 meses.</v>
@@ -654,7 +654,7 @@
         <v>no</v>
       </c>
       <c r="T3" t="str">
-        <v>https://images.samsung.com/is/image/samsung/latin-en-ms23k3513aw-zl-001-front-white.jpg|https://images.samsung.com/is/image/samsung/latin-en-ms23k3513aw-zl-002-front-open-white.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Microwave_oven.jpg|https://upload.wikimedia.org/wikipedia/commons/b/bb/Microwave_Oven.jpg</v>
       </c>
       <c r="U3" t="str">
         <v>Microondas Samsung MS23K3513AW de 23 litros y 1150 watts. Panel de control con perillas de tiempo y potencia. 5 niveles de potencia ajustables. Funcion de descongelado automatico por peso. Plato giratorio de vidrio de 28.8 cm de diametro. Incluye garantia oficial Samsung de 12 meses.</v>
@@ -690,7 +690,7 @@
   <dimension ref="A1:E40"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="2" max="2" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,128 +705,140 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Generado: 2026-05-12T15:54:17.353Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>IMPORTANTE — LEER ANTES DE USAR</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>IMPORTANTE — LEER ANTES DE USAR</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1. Este archivo esta disenado para pruebas de publicacion REAL en Mercado Libre.</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2. Usar UNICAMENTE con MERCADOLIBRE_DRY_RUN=false (publicacion real activada).</v>
+        <v>1. Este archivo esta disenado para pruebas de publicacion REAL en Mercado Libre.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3. Publicar DE A UNO primero para verificar que ML acepta el payload.</v>
+        <v>2. Usar UNICAMENTE con MERCADOLIBRE_DRY_RUN=false (publicacion real activada).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4. Las imagenes DEBEN ser URLs HTTPS publicamente accesibles por ML.</v>
+        <v>3. Las imagenes fueron verificadas HTTP 200 al momento de generar este archivo.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">   Verificar cada URL abriendo en el navegador antes de publicar.</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>PRODUCTOS INCLUIDOS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>PRODUCTOS INCLUIDOS</v>
+        <v>Fila</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Producto</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Marca</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Categoria esperada</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Precio ARS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Fila</v>
+        <v>2</v>
       </c>
       <c r="B13" t="str">
-        <v>Producto</v>
+        <v>Heladera Samsung No Frost 290L Blanca</v>
       </c>
       <c r="C13" t="str">
-        <v>Marca</v>
+        <v>Samsung</v>
       </c>
       <c r="D13" t="str">
-        <v>Categoria esperada</v>
+        <v>MLA-REFRIGERATORS</v>
       </c>
       <c r="E13" t="str">
-        <v>Precio ARS</v>
+        <v>450.000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="str">
-        <v>Heladera Samsung No Frost 290L Blanca</v>
+        <v>Microondas Samsung 23L 1150W Blanco</v>
       </c>
       <c r="C14" t="str">
         <v>Samsung</v>
       </c>
       <c r="D14" t="str">
-        <v>MLA-REFRIGERATORS</v>
+        <v>MLA-MICROWAVES</v>
       </c>
       <c r="E14" t="str">
-        <v>450.000</v>
+        <v>115.000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Microondas Samsung 23L 1150W Blanco</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Samsung</v>
-      </c>
-      <c r="D15" t="str">
-        <v>MLA-MICROWAVES</v>
-      </c>
-      <c r="E15" t="str">
-        <v>115.000</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>IMAGENES VERIFICADAS (HTTP 200 al generar)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>IMAGENES — VERIFICAR ACCESIBILIDAD</v>
+        <v>Heladera img1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/8/89/Refrigerator.jpg</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Las imagenes usan el CDN oficial de Samsung (images.samsung.com).</v>
+        <v>Heladera img2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/b8/Fridge.jpg</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Si las URLs no cargan (404), reemplazarlas con fotos del producto en hosting propio.</v>
+        <v>Microondas img1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Microwave_oven.jpg</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Formato recomendado por ML: HTTPS, JPG o PNG, minimo 500x500px.</v>
+        <v>Microondas img2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/b/bb/Microwave_Oven.jpg</v>
       </c>
     </row>
     <row r="21">
